--- a/artfynd/A 15831-2026 artfynd.xlsx
+++ b/artfynd/A 15831-2026 artfynd.xlsx
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>94523134</v>
+        <v>91953585</v>
       </c>
       <c r="B2" t="n">
-        <v>91905</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Torshöjden - Sörrun, Jmt</t>
+          <t>Jämtlands län, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>463867</v>
+        <v>463758</v>
       </c>
       <c r="R2" t="n">
-        <v>7104904</v>
+        <v>7104259</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
+          <t>2019-10-31</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Garnlavsrikt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,27 +770,31 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94523134</t>
+          <t>https://artportalen.se/Sighting/91953585</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94523145</v>
+        <v>94489368</v>
       </c>
       <c r="B3" t="n">
-        <v>91923</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +802,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Torshöjden - Sörrun, Jmt</t>
+          <t>Krokom, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>463831</v>
+        <v>464028</v>
       </c>
       <c r="R3" t="n">
-        <v>7104886</v>
+        <v>7104460</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,56 +871,55 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94523145</t>
+          <t>https://artportalen.se/Sighting/94489368</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>94523116</v>
+        <v>94523140</v>
       </c>
       <c r="B4" t="n">
-        <v>99140</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>463869</v>
+        <v>463815</v>
       </c>
       <c r="R4" t="n">
-        <v>7104916</v>
+        <v>7104262</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,54 +990,54 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94523116</t>
+          <t>https://artportalen.se/Sighting/94523140</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>94523143</v>
+        <v>91847585</v>
       </c>
       <c r="B5" t="n">
-        <v>79327</v>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Torshöjden - Sörrun, Jmt</t>
+          <t>Jämtlands län, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464003</v>
+        <v>464448</v>
       </c>
       <c r="R5" t="n">
-        <v>7104699</v>
+        <v>7104160</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1052,12 +1061,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
+          <t>2019-10-31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1072,27 +1081,31 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94523143</t>
+          <t>https://artportalen.se/Sighting/91847585</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>94580775</v>
+        <v>91847627</v>
       </c>
       <c r="B6" t="n">
-        <v>99140</v>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,37 +1113,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Myhrbodarna, Valsjöbyn, Jmt, Jmt</t>
+          <t>Jämtlands län, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464051</v>
+        <v>464390</v>
       </c>
       <c r="R6" t="n">
-        <v>7104632</v>
+        <v>7104188</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1154,12 +1167,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
+          <t>2019-10-31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1174,62 +1187,67 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lisa Johansson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94580775</t>
+          <t>https://artportalen.se/Sighting/91847627</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>91847572</v>
+        <v>94489320</v>
       </c>
       <c r="B7" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Krokom, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464719</v>
+        <v>463973</v>
       </c>
       <c r="R7" t="n">
-        <v>7104715</v>
+        <v>7104541</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1256,12 +1274,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1281,23 +1299,19 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91847572</t>
+          <t>https://artportalen.se/Sighting/94489320</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>91847547</v>
+        <v>91847584</v>
       </c>
       <c r="B8" t="n">
         <v>80461</v>
@@ -1332,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464705</v>
+        <v>464448</v>
       </c>
       <c r="R8" t="n">
-        <v>7104752</v>
+        <v>7104160</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1397,16 +1411,16 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91847547</t>
+          <t>https://artportalen.se/Sighting/91847584</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>91847571</v>
+        <v>94489530</v>
       </c>
       <c r="B9" t="n">
-        <v>80461</v>
+        <v>57141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1414,34 +1428,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Krokom, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464719</v>
+        <v>464271</v>
       </c>
       <c r="R9" t="n">
-        <v>7104715</v>
+        <v>7104281</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1468,12 +1485,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1493,26 +1510,22 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91847571</t>
+          <t>https://artportalen.se/Sighting/94489530</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>91847574</v>
+        <v>94489922</v>
       </c>
       <c r="B10" t="n">
-        <v>80467</v>
+        <v>99140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1520,34 +1533,36 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Krokom, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464719</v>
+        <v>464228</v>
       </c>
       <c r="R10" t="n">
-        <v>7104715</v>
+        <v>7104382</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1574,12 +1589,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1599,26 +1614,22 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91847574</t>
+          <t>https://artportalen.se/Sighting/94489922</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>91847573</v>
+        <v>94489481</v>
       </c>
       <c r="B11" t="n">
-        <v>80468</v>
+        <v>99038</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1626,34 +1637,32 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>223597</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Krokom, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464719</v>
+        <v>464221</v>
       </c>
       <c r="R11" t="n">
-        <v>7104715</v>
+        <v>7104290</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1680,12 +1689,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1705,64 +1714,60 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91847573</t>
+          <t>https://artportalen.se/Sighting/94489481</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>94580779</v>
+        <v>94523134</v>
       </c>
       <c r="B12" t="n">
-        <v>99022</v>
+        <v>91905</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220093</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Myhrbodarna, Valsjöbyn, Jmt, Jmt</t>
+          <t>Torshöjden - Sörrun, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464563</v>
+        <v>463867</v>
       </c>
       <c r="R12" t="n">
-        <v>7104663</v>
+        <v>7104904</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1811,60 +1816,60 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lisa Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94580779</t>
+          <t>https://artportalen.se/Sighting/94523134</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>91847585</v>
+        <v>94523143</v>
       </c>
       <c r="B13" t="n">
-        <v>80433</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Torshöjden - Sörrun, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464448</v>
+        <v>464003</v>
       </c>
       <c r="R13" t="n">
-        <v>7104160</v>
+        <v>7104699</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1888,12 +1893,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1908,31 +1913,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91847585</t>
+          <t>https://artportalen.se/Sighting/94523143</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>91847627</v>
+        <v>94523116</v>
       </c>
       <c r="B14" t="n">
-        <v>91872</v>
+        <v>99140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1940,37 +1941,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Torshöjden - Sörrun, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464390</v>
+        <v>463869</v>
       </c>
       <c r="R14" t="n">
-        <v>7104188</v>
+        <v>7104916</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1994,12 +1995,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2014,69 +2015,65 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91847627</t>
+          <t>https://artportalen.se/Sighting/94523116</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>91953585</v>
+        <v>94580775</v>
       </c>
       <c r="B15" t="n">
-        <v>79327</v>
+        <v>99140</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Myhrbodarna, Valsjöbyn, Jmt, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>463758</v>
+        <v>464051</v>
       </c>
       <c r="R15" t="n">
-        <v>7104259</v>
+        <v>7104632</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2100,17 +2097,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Garnlavsrikt</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2125,67 +2117,62 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Lisa Johansson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91953585</t>
+          <t>https://artportalen.se/Sighting/94580775</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>94489320</v>
+        <v>91847572</v>
       </c>
       <c r="B16" t="n">
-        <v>79327</v>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Krokom, Jmt</t>
+          <t>Jämtlands län, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>463973</v>
+        <v>464719</v>
       </c>
       <c r="R16" t="n">
-        <v>7104541</v>
+        <v>7104715</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2212,12 +2199,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
+          <t>2019-10-31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2237,58 +2224,61 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94489320</t>
+          <t>https://artportalen.se/Sighting/91847572</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>94489368</v>
+        <v>91847547</v>
       </c>
       <c r="B17" t="n">
-        <v>79327</v>
+        <v>80461</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Krokom, Jmt</t>
+          <t>Jämtlands län, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464028</v>
+        <v>464705</v>
       </c>
       <c r="R17" t="n">
-        <v>7104460</v>
+        <v>7104752</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2315,12 +2305,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
+          <t>2019-10-31</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2340,60 +2330,64 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94489368</t>
+          <t>https://artportalen.se/Sighting/91847547</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>94523140</v>
+        <v>91847571</v>
       </c>
       <c r="B18" t="n">
-        <v>79327</v>
+        <v>80461</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Torshöjden - Sörrun, Jmt</t>
+          <t>Jämtlands län, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463815</v>
+        <v>464719</v>
       </c>
       <c r="R18" t="n">
-        <v>7104262</v>
+        <v>7104715</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2417,12 +2411,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
+          <t>2019-10-31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2437,27 +2431,31 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94523140</t>
+          <t>https://artportalen.se/Sighting/91847571</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>91847584</v>
+        <v>91847574</v>
       </c>
       <c r="B19" t="n">
-        <v>80461</v>
+        <v>80467</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2465,21 +2463,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2489,10 +2487,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464448</v>
+        <v>464719</v>
       </c>
       <c r="R19" t="n">
-        <v>7104160</v>
+        <v>7104715</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2554,16 +2552,16 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91847584</t>
+          <t>https://artportalen.se/Sighting/91847574</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>94489530</v>
+        <v>91847573</v>
       </c>
       <c r="B20" t="n">
-        <v>57141</v>
+        <v>80468</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2571,37 +2569,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>6464</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Krokom, Jmt</t>
+          <t>Jämtlands län, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464271</v>
+        <v>464719</v>
       </c>
       <c r="R20" t="n">
-        <v>7104281</v>
+        <v>7104715</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2628,12 +2623,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
+          <t>2019-10-31</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2653,22 +2648,26 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94489530</t>
+          <t>https://artportalen.se/Sighting/91847573</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>94489922</v>
+        <v>94580779</v>
       </c>
       <c r="B21" t="n">
-        <v>99140</v>
+        <v>99022</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2676,39 +2675,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Krokom, Jmt</t>
+          <t>Myhrbodarna, Valsjöbyn, Jmt, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464228</v>
+        <v>464563</v>
       </c>
       <c r="R21" t="n">
-        <v>7104382</v>
+        <v>7104663</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2752,63 +2749,65 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lisa Johansson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94489922</t>
+          <t>https://artportalen.se/Sighting/94580779</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>94489481</v>
+        <v>94523145</v>
       </c>
       <c r="B22" t="n">
-        <v>99038</v>
+        <v>91923</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>223597</v>
+        <v>1204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Krokom, Jmt</t>
+          <t>Torshöjden - Sörrun, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464221</v>
+        <v>463831</v>
       </c>
       <c r="R22" t="n">
-        <v>7104290</v>
+        <v>7104886</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2846,24 +2845,25 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94489481</t>
+          <t>https://artportalen.se/Sighting/94523145</t>
         </is>
       </c>
     </row>
